--- a/Experiences/Mesures temporelles.xlsx
+++ b/Experiences/Mesures temporelles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A022001-6793-4953-B98F-E8BDFB581C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E11DE9E-6C52-460C-8733-C1008DDC95FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="13">
   <si>
     <t>m [kg]</t>
   </si>
@@ -226,10 +226,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$B$2:$B$10</c:f>
+              <c:f>Feuil1!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -256,16 +256,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$2:$C$10</c:f>
+              <c:f>Feuil1!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>9.4</c:v>
                 </c:pt>
@@ -288,10 +291,13 @@
                   <c:v>23.46</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>23.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>23.88</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.5</c:v>
+                <c:pt idx="9">
+                  <c:v>24.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -335,10 +341,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$B$11:$B$19</c:f>
+              <c:f>Feuil1!$B$12:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -365,16 +371,19 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1362</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$11:$C$19</c:f>
+              <c:f>Feuil1!$C$12:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>12.08</c:v>
                 </c:pt>
@@ -401,6 +410,9 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>23.16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1332,16 +1344,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>147654</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>659751</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>137174</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>21098</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>157043</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>143387</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1666,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E30E31B0-7DB1-41AB-9A01-4B635A940C31}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -1957,7 +1969,7 @@
         <v>324</v>
       </c>
       <c r="C9">
-        <v>23.88</v>
+        <v>23.5</v>
       </c>
       <c r="D9" s="1">
         <v>9.5000000000000005E-5</v>
@@ -1992,7 +2004,7 @@
         <v>375</v>
       </c>
       <c r="C10">
-        <v>23.5</v>
+        <v>23.88</v>
       </c>
       <c r="D10" s="1">
         <v>9.5000000000000005E-5</v>
@@ -2021,22 +2033,35 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <f>22*60+42</f>
+        <v>1362</v>
       </c>
       <c r="C11">
-        <v>12.08</v>
+        <v>24.4</v>
       </c>
       <c r="D11" s="1">
-        <v>5.5000000000000002E-5</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="E11" s="1">
-        <v>5.0017199999999998E-2</v>
+        <v>5.0005500000000001E-2</v>
       </c>
       <c r="F11" s="1">
-        <v>1009</v>
+        <v>1270</v>
+      </c>
+      <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
+        <v>90</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="J11" s="1">
+        <v>907</v>
       </c>
       <c r="K11" s="1">
         <v>9.81</v>
@@ -2047,10 +2072,34 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>20.399999999999999</v>
+        <v>12.08</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E12" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G12" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H12" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J12" s="1">
+        <v>800</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9.81</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -2058,10 +2107,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>22.32</v>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E13" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G13" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H13" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J13" s="1">
+        <v>800</v>
+      </c>
+      <c r="K13" s="1">
+        <v>9.81</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -2069,10 +2142,34 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>23.21</v>
+        <v>22.32</v>
+      </c>
+      <c r="D14" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H14" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J14" s="1">
+        <v>800</v>
+      </c>
+      <c r="K14" s="1">
+        <v>9.81</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -2080,10 +2177,34 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="C15">
-        <v>23.17</v>
+        <v>23.21</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G15" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H15" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J15" s="1">
+        <v>800</v>
+      </c>
+      <c r="K15" s="1">
+        <v>9.81</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -2091,43 +2212,209 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="C16">
-        <v>23.04</v>
+        <v>23.17</v>
+      </c>
+      <c r="D16" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E16" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G16" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H16" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J16" s="1">
+        <v>800</v>
+      </c>
+      <c r="K16" s="1">
+        <v>9.81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
       <c r="B17">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="C17">
-        <v>22.9</v>
+        <v>23.04</v>
+      </c>
+      <c r="D17" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G17" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H17" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J17" s="1">
+        <v>800</v>
+      </c>
+      <c r="K17" s="1">
+        <v>9.81</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
       <c r="B18">
-        <v>324</v>
+        <v>266</v>
       </c>
       <c r="C18">
-        <v>23.19</v>
+        <v>22.9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G18" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H18" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J18" s="1">
+        <v>800</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9.81</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>12</v>
       </c>
       <c r="B19">
+        <v>324</v>
+      </c>
+      <c r="C19">
+        <v>23.19</v>
+      </c>
+      <c r="D19" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G19" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H19" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J19" s="1">
+        <v>800</v>
+      </c>
+      <c r="K19" s="1">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20">
         <v>375</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>23.16</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G20" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H20" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J20" s="1">
+        <v>800</v>
+      </c>
+      <c r="K20" s="1">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21">
+        <v>1362</v>
+      </c>
+      <c r="C21">
+        <v>23.26</v>
+      </c>
+      <c r="D21" s="1">
+        <v>5.5000000000000002E-5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>5.0017199999999998E-2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1009</v>
+      </c>
+      <c r="G21" s="1">
+        <v>12.164</v>
+      </c>
+      <c r="H21" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J21" s="1">
+        <v>800</v>
+      </c>
+      <c r="K21" s="1">
+        <v>9.81</v>
       </c>
     </row>
   </sheetData>

--- a/Experiences/Mesures temporelles.xlsx
+++ b/Experiences/Mesures temporelles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E11DE9E-6C52-460C-8733-C1008DDC95FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349A98CC-BC8A-4662-8ABD-DF04F2683941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
   </bookViews>

--- a/Experiences/Mesures temporelles.xlsx
+++ b/Experiences/Mesures temporelles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349A98CC-BC8A-4662-8ABD-DF04F2683941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE59D0-B2BA-474E-B8D2-D0B6F44206C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>

--- a/Experiences/Mesures temporelles.xlsx
+++ b/Experiences/Mesures temporelles.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABE59D0-B2BA-474E-B8D2-D0B6F44206C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB11AA91-1AEB-409C-A943-70EA0EDF53E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CA835191-6F9F-433F-956F-85250E445344}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="13">
   <si>
     <t>m [kg]</t>
   </si>
@@ -190,7 +191,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12919311500896699"/>
+          <c:y val="0.13424025101490331"/>
+          <c:w val="0.79215949082268422"/>
+          <c:h val="0.7050503639972584"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
@@ -226,10 +237,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$B$2:$B$11</c:f>
+              <c:f>Feuil1!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -251,24 +262,15 @@
                 <c:pt idx="6">
                   <c:v>266</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>324</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>375</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1362</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$2:$C$11</c:f>
+              <c:f>Feuil1!$C$2:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>9.4</c:v>
                 </c:pt>
@@ -289,15 +291,6 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>23.46</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>23.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.88</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>24.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -341,10 +334,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$B$12:$B$21</c:f>
+              <c:f>Feuil1!$B$12:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -366,24 +359,15 @@
                 <c:pt idx="6">
                   <c:v>266</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>324</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>375</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1362</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$12:$C$21</c:f>
+              <c:f>Feuil1!$C$12:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>12.08</c:v>
                 </c:pt>
@@ -404,15 +388,6 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>22.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>23.19</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.16</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>23.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -711,6 +686,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.62540663166854737"/>
+          <c:y val="0.66348385772972296"/>
+          <c:w val="0.29160699911028265"/>
+          <c:h val="0.15472640714970695"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1344,16 +1329,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>659751</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>137174</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>202278</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>144002</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>157043</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>143387</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>27311</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>20484</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1678,10 +1663,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E30E31B0-7DB1-41AB-9A01-4B635A940C31}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1716,7 +1701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1745,13 +1730,16 @@
         <v>0.4</v>
       </c>
       <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="L2" s="1">
         <v>907</v>
       </c>
-      <c r="K2" s="1">
-        <v>9.81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1780,13 +1768,13 @@
         <v>0.4</v>
       </c>
       <c r="J3" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1815,13 +1803,13 @@
         <v>0.4</v>
       </c>
       <c r="J4" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1850,13 +1838,13 @@
         <v>0.4</v>
       </c>
       <c r="J5" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1885,13 +1873,13 @@
         <v>0.4</v>
       </c>
       <c r="J6" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1920,13 +1908,13 @@
         <v>0.4</v>
       </c>
       <c r="J7" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1955,13 +1943,13 @@
         <v>0.4</v>
       </c>
       <c r="J8" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1990,13 +1978,13 @@
         <v>0.4</v>
       </c>
       <c r="J9" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2025,13 +2013,13 @@
         <v>0.4</v>
       </c>
       <c r="J10" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2061,13 +2049,13 @@
         <v>0.4</v>
       </c>
       <c r="J11" s="1">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2096,13 +2084,16 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9.81</v>
+      </c>
+      <c r="L12" s="1">
         <v>800</v>
       </c>
-      <c r="K12" s="1">
-        <v>9.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2131,13 +2122,13 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J13" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -2166,13 +2157,13 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J14" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -2201,13 +2192,13 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J15" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
         <v>9.81</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2236,7 +2227,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J16" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
         <v>9.81</v>
@@ -2271,7 +2262,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J17" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
         <v>9.81</v>
@@ -2306,7 +2297,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J18" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
         <v>9.81</v>
@@ -2341,7 +2332,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J19" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
         <v>9.81</v>
@@ -2376,7 +2367,7 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J20" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>9.81</v>
@@ -2411,9 +2402,674 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="J21" s="1">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>9.6</v>
+      </c>
+      <c r="D22" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G22">
+        <v>15</v>
+      </c>
+      <c r="H22">
+        <v>90</v>
+      </c>
+      <c r="I22">
+        <v>0.4</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>15.24</v>
+      </c>
+      <c r="D23" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>90</v>
+      </c>
+      <c r="I23">
+        <v>0.4</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D24" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24">
+        <v>90</v>
+      </c>
+      <c r="I24">
+        <v>0.4</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D25" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G25">
+        <v>15</v>
+      </c>
+      <c r="H25">
+        <v>90</v>
+      </c>
+      <c r="I25">
+        <v>0.4</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>18.27</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G26">
+        <v>15</v>
+      </c>
+      <c r="H26">
+        <v>90</v>
+      </c>
+      <c r="I26">
+        <v>0.4</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>19.5</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G27">
+        <v>15</v>
+      </c>
+      <c r="H27">
+        <v>90</v>
+      </c>
+      <c r="I27">
+        <v>0.4</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G28">
+        <v>15</v>
+      </c>
+      <c r="H28">
+        <v>90</v>
+      </c>
+      <c r="I28">
+        <v>0.4</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>20.48</v>
+      </c>
+      <c r="D29" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>90</v>
+      </c>
+      <c r="I29">
+        <v>0.4</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>20</v>
+      </c>
+      <c r="C30">
+        <v>21.04</v>
+      </c>
+      <c r="D30" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+      <c r="H30">
+        <v>90</v>
+      </c>
+      <c r="I30">
+        <v>0.4</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>24</v>
+      </c>
+      <c r="C31">
+        <v>21.48</v>
+      </c>
+      <c r="D31" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G31">
+        <v>15</v>
+      </c>
+      <c r="H31">
+        <v>90</v>
+      </c>
+      <c r="I31">
+        <v>0.4</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>21.99</v>
+      </c>
+      <c r="D32" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G32">
+        <v>15</v>
+      </c>
+      <c r="H32">
+        <v>90</v>
+      </c>
+      <c r="I32">
+        <v>0.4</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33">
+        <v>94</v>
+      </c>
+      <c r="C33">
+        <v>22.56</v>
+      </c>
+      <c r="D33" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G33">
+        <v>15</v>
+      </c>
+      <c r="H33">
+        <v>90</v>
+      </c>
+      <c r="I33">
+        <v>0.4</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <v>209</v>
+      </c>
+      <c r="C34">
+        <v>22.8</v>
+      </c>
+      <c r="D34" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G34">
+        <v>15</v>
+      </c>
+      <c r="H34">
+        <v>90</v>
+      </c>
+      <c r="I34">
+        <v>0.4</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <v>277</v>
+      </c>
+      <c r="C35">
+        <v>22.91</v>
+      </c>
+      <c r="D35" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G35">
+        <v>15</v>
+      </c>
+      <c r="H35">
+        <v>90</v>
+      </c>
+      <c r="I35">
+        <v>0.4</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36">
+        <v>1434</v>
+      </c>
+      <c r="C36">
+        <v>24.5</v>
+      </c>
+      <c r="D36" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>90</v>
+      </c>
+      <c r="I36">
+        <v>0.4</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37">
+        <v>1522</v>
+      </c>
+      <c r="C37">
+        <v>24.55</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G37">
+        <v>15</v>
+      </c>
+      <c r="H37">
+        <v>90</v>
+      </c>
+      <c r="I37">
+        <v>0.4</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>1605</v>
+      </c>
+      <c r="C38">
+        <v>24.5</v>
+      </c>
+      <c r="D38" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+      <c r="H38">
+        <v>90</v>
+      </c>
+      <c r="I38">
+        <v>0.4</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39">
+        <v>1869</v>
+      </c>
+      <c r="C39">
+        <v>24.61</v>
+      </c>
+      <c r="D39" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G39">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>90</v>
+      </c>
+      <c r="I39">
+        <v>0.4</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>2848</v>
+      </c>
+      <c r="C40">
+        <v>24.61</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9.5000000000000005E-5</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1270</v>
+      </c>
+      <c r="G40">
+        <v>15</v>
+      </c>
+      <c r="H40">
+        <v>90</v>
+      </c>
+      <c r="I40">
+        <v>0.4</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
         <v>9.81</v>
       </c>
     </row>
